--- a/main/ig/ValueSet-fr-core-vs-organization-uac-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-organization-uac-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-organization-uac-type.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-organization-uac-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
